--- a/veriler.xlsx
+++ b/veriler.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\furka\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\furka\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FCB5E45-7BAB-4E97-BC73-6DEEA0E19B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3192903B-D74C-4BB1-913C-A87A9B0C8CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Yapılandırma" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hizmetler!$A$1:$I$555</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hizmetler!$A$1:$I$540</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5045" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4910" uniqueCount="308">
   <si>
     <t>Müdürlük</t>
   </si>
@@ -682,21 +682,6 @@
     <t>En Az %40 Engel Oranı</t>
   </si>
   <si>
-    <t>Kadın Aile Hizmetleri Müdürlüğü</t>
-  </si>
-  <si>
-    <t>İstanbul Aile Danışmanlık ve Eğitim Merkezi</t>
-  </si>
-  <si>
-    <t>Kadın Danışma Birimi</t>
-  </si>
-  <si>
-    <t>Mahalle Evi</t>
-  </si>
-  <si>
-    <t>Kadın Emeği Üretim Atölyesi</t>
-  </si>
-  <si>
     <t>İstanbul Senin Uygulamasına Kayıt Olmak</t>
   </si>
   <si>
@@ -959,9 +944,6 @@
   </si>
   <si>
     <t>Toplam Gelir 2 Asgari Ücret Altı Veya Kişi Başı Gelir Asgari Ücret 1/2</t>
-  </si>
-  <si>
-    <t>İbb Kadın</t>
   </si>
   <si>
     <t>İbb Çocuk</t>
@@ -1279,7 +1261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1452"/>
+  <dimension ref="A1:Q1437"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.6640625" customWidth="1"/>
@@ -1398,7 +1380,7 @@
         <v>22</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>15</v>
@@ -1473,7 +1455,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>11</v>
@@ -1502,7 +1484,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>11</v>
@@ -1514,7 +1496,7 @@
         <v>22</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>15</v>
@@ -1531,7 +1513,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>11</v>
@@ -1560,7 +1542,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>11</v>
@@ -1572,7 +1554,7 @@
         <v>29</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>15</v>
@@ -1630,7 +1612,7 @@
         <v>22</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>15</v>
@@ -1868,7 +1850,7 @@
         <v>53</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>54</v>
@@ -1897,7 +1879,7 @@
         <v>55</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>54</v>
@@ -1920,7 +1902,7 @@
         <v>22</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>15</v>
@@ -2065,7 +2047,7 @@
         <v>39</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>15</v>
@@ -2094,7 +2076,7 @@
         <v>61</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>15</v>
@@ -2123,7 +2105,7 @@
         <v>41</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>15</v>
@@ -2152,7 +2134,7 @@
         <v>62</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>63</v>
@@ -2239,7 +2221,7 @@
         <v>19</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>15</v>
@@ -2268,7 +2250,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>15</v>
@@ -2355,7 +2337,7 @@
         <v>70</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>15</v>
@@ -2384,7 +2366,7 @@
         <v>71</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>15</v>
@@ -2587,7 +2569,7 @@
         <v>82</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>83</v>
@@ -2645,7 +2627,7 @@
         <v>86</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>81</v>
@@ -2674,7 +2656,7 @@
         <v>86</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>87</v>
@@ -2761,7 +2743,7 @@
         <v>19</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>15</v>
@@ -2778,7 +2760,7 @@
         <v>30</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>11</v>
@@ -2807,7 +2789,7 @@
         <v>30</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>11</v>
@@ -2819,7 +2801,7 @@
         <v>22</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>15</v>
@@ -2836,7 +2818,7 @@
         <v>30</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>11</v>
@@ -2865,7 +2847,7 @@
         <v>30</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>11</v>
@@ -2894,7 +2876,7 @@
         <v>30</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>11</v>
@@ -2906,7 +2888,7 @@
         <v>70</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>15</v>
@@ -2923,7 +2905,7 @@
         <v>30</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>11</v>
@@ -2935,7 +2917,7 @@
         <v>71</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>15</v>
@@ -2952,7 +2934,7 @@
         <v>30</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>11</v>
@@ -2981,7 +2963,7 @@
         <v>30</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>11</v>
@@ -3010,7 +2992,7 @@
         <v>30</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>11</v>
@@ -3022,7 +3004,7 @@
         <v>19</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>15</v>
@@ -3039,7 +3021,7 @@
         <v>30</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>51</v>
@@ -3109,7 +3091,7 @@
         <v>22</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>15</v>
@@ -3167,7 +3149,7 @@
         <v>39</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>15</v>
@@ -3196,7 +3178,7 @@
         <v>41</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>15</v>
@@ -3225,7 +3207,7 @@
         <v>61</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>15</v>
@@ -3283,7 +3265,7 @@
         <v>61</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>15</v>
@@ -3312,7 +3294,7 @@
         <v>62</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>15</v>
@@ -3341,7 +3323,7 @@
         <v>62</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>63</v>
@@ -3434,7 +3416,7 @@
         <v>55</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>54</v>
@@ -3463,7 +3445,7 @@
         <v>55</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>54</v>
@@ -3492,7 +3474,7 @@
         <v>55</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>64</v>
@@ -3521,7 +3503,7 @@
         <v>53</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>54</v>
@@ -3573,7 +3555,7 @@
         <v>22</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>15</v>
@@ -3805,7 +3787,7 @@
         <v>22</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>15</v>
@@ -3892,7 +3874,7 @@
         <v>22</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>15</v>
@@ -4008,7 +3990,7 @@
         <v>22</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>15</v>
@@ -4095,7 +4077,7 @@
         <v>22</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>15</v>
@@ -4153,7 +4135,7 @@
         <v>39</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>15</v>
@@ -4182,7 +4164,7 @@
         <v>41</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>15</v>
@@ -4240,7 +4222,7 @@
         <v>62</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>15</v>
@@ -4414,7 +4396,7 @@
         <v>58</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>125</v>
@@ -4443,7 +4425,7 @@
         <v>45</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>133</v>
@@ -4472,7 +4454,7 @@
         <v>45</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>134</v>
@@ -4501,7 +4483,7 @@
         <v>45</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>135</v>
@@ -4530,7 +4512,7 @@
         <v>45</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>129</v>
@@ -4559,7 +4541,7 @@
         <v>45</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>136</v>
@@ -4588,7 +4570,7 @@
         <v>45</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>137</v>
@@ -4617,7 +4599,7 @@
         <v>62</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>138</v>
@@ -4646,7 +4628,7 @@
         <v>62</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>125</v>
@@ -4672,7 +4654,7 @@
         <v>140</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>141</v>
@@ -4701,7 +4683,7 @@
         <v>140</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>142</v>
@@ -4791,7 +4773,7 @@
         <v>22</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>15</v>
@@ -4878,7 +4860,7 @@
         <v>22</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>15</v>
@@ -4907,7 +4889,7 @@
         <v>39</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>15</v>
@@ -4965,7 +4947,7 @@
         <v>62</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>15</v>
@@ -5139,7 +5121,7 @@
         <v>45</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>133</v>
@@ -5168,7 +5150,7 @@
         <v>45</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>134</v>
@@ -5197,7 +5179,7 @@
         <v>45</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>135</v>
@@ -5226,7 +5208,7 @@
         <v>45</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>129</v>
@@ -5255,7 +5237,7 @@
         <v>45</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>136</v>
@@ -5284,7 +5266,7 @@
         <v>62</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>138</v>
@@ -5313,7 +5295,7 @@
         <v>62</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>125</v>
@@ -5339,7 +5321,7 @@
         <v>140</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>141</v>
@@ -5368,7 +5350,7 @@
         <v>140</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>142</v>
@@ -5400,7 +5382,7 @@
         <v>58</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>125</v>
@@ -5429,7 +5411,7 @@
         <v>45</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>137</v>
@@ -5545,7 +5527,7 @@
         <v>22</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>15</v>
@@ -5574,7 +5556,7 @@
         <v>39</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>15</v>
@@ -5603,7 +5585,7 @@
         <v>41</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>15</v>
@@ -5661,7 +5643,7 @@
         <v>62</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>15</v>
@@ -5835,7 +5817,7 @@
         <v>45</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>133</v>
@@ -5864,7 +5846,7 @@
         <v>45</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>134</v>
@@ -5893,7 +5875,7 @@
         <v>45</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>135</v>
@@ -5922,7 +5904,7 @@
         <v>45</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>129</v>
@@ -5951,7 +5933,7 @@
         <v>45</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>136</v>
@@ -5980,7 +5962,7 @@
         <v>45</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>137</v>
@@ -6009,7 +5991,7 @@
         <v>62</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>138</v>
@@ -6038,7 +6020,7 @@
         <v>62</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>125</v>
@@ -6064,7 +6046,7 @@
         <v>140</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>141</v>
@@ -6093,7 +6075,7 @@
         <v>140</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>142</v>
@@ -6125,7 +6107,7 @@
         <v>58</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>125</v>
@@ -6212,7 +6194,7 @@
         <v>22</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>15</v>
@@ -6270,7 +6252,7 @@
         <v>22</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>15</v>
@@ -6328,7 +6310,7 @@
         <v>39</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>15</v>
@@ -6357,7 +6339,7 @@
         <v>41</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>15</v>
@@ -6386,7 +6368,7 @@
         <v>61</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>15</v>
@@ -6444,7 +6426,7 @@
         <v>61</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>15</v>
@@ -6473,7 +6455,7 @@
         <v>62</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>15</v>
@@ -6531,7 +6513,7 @@
         <v>39</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>15</v>
@@ -6560,7 +6542,7 @@
         <v>62</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>63</v>
@@ -6653,7 +6635,7 @@
         <v>55</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I185" s="2" t="s">
         <v>54</v>
@@ -6682,7 +6664,7 @@
         <v>55</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I186" s="2" t="s">
         <v>54</v>
@@ -6711,7 +6693,7 @@
         <v>55</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I187" s="2" t="s">
         <v>64</v>
@@ -6740,7 +6722,7 @@
         <v>53</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I188" s="2" t="s">
         <v>54</v>
@@ -6821,7 +6803,7 @@
         <v>22</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>15</v>
@@ -6966,7 +6948,7 @@
         <v>22</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>15</v>
@@ -6983,7 +6965,7 @@
         <v>30</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>11</v>
@@ -7012,7 +6994,7 @@
         <v>30</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>11</v>
@@ -7024,7 +7006,7 @@
         <v>22</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G198" s="1" t="s">
         <v>15</v>
@@ -7041,7 +7023,7 @@
         <v>30</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>11</v>
@@ -7070,7 +7052,7 @@
         <v>30</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>11</v>
@@ -7082,7 +7064,7 @@
         <v>70</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="G200" s="1" t="s">
         <v>15</v>
@@ -7099,7 +7081,7 @@
         <v>30</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>11</v>
@@ -7128,7 +7110,7 @@
         <v>30</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>11</v>
@@ -7157,7 +7139,7 @@
         <v>30</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>11</v>
@@ -7186,7 +7168,7 @@
         <v>30</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>11</v>
@@ -7198,7 +7180,7 @@
         <v>85</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>15</v>
@@ -7223,7 +7205,7 @@
         <v>30</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>11</v>
@@ -7252,7 +7234,7 @@
         <v>30</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>11</v>
@@ -7264,7 +7246,7 @@
         <v>22</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>15</v>
@@ -7281,7 +7263,7 @@
         <v>30</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>11</v>
@@ -7310,7 +7292,7 @@
         <v>30</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>43</v>
@@ -7322,7 +7304,7 @@
         <v>41</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>15</v>
@@ -7339,7 +7321,7 @@
         <v>30</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>43</v>
@@ -7351,7 +7333,7 @@
         <v>39</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>15</v>
@@ -7368,7 +7350,7 @@
         <v>30</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>43</v>
@@ -7380,7 +7362,7 @@
         <v>41</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G210" s="1" t="s">
         <v>15</v>
@@ -7397,7 +7379,7 @@
         <v>30</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>43</v>
@@ -7409,7 +7391,7 @@
         <v>61</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="G211" s="1" t="s">
         <v>15</v>
@@ -7426,7 +7408,7 @@
         <v>30</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>43</v>
@@ -7455,7 +7437,7 @@
         <v>30</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>43</v>
@@ -7467,7 +7449,7 @@
         <v>61</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>15</v>
@@ -7484,7 +7466,7 @@
         <v>30</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>43</v>
@@ -7496,7 +7478,7 @@
         <v>62</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>15</v>
@@ -7513,7 +7495,7 @@
         <v>30</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>51</v>
@@ -7531,7 +7513,7 @@
         <v>55</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I215" s="2" t="s">
         <v>54</v>
@@ -7542,7 +7524,7 @@
         <v>30</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>51</v>
@@ -7554,7 +7536,7 @@
         <v>62</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>63</v>
@@ -7571,7 +7553,7 @@
         <v>30</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>51</v>
@@ -7600,7 +7582,7 @@
         <v>30</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>51</v>
@@ -7629,7 +7611,7 @@
         <v>30</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>51</v>
@@ -7647,7 +7629,7 @@
         <v>55</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I219" s="2" t="s">
         <v>54</v>
@@ -7658,7 +7640,7 @@
         <v>30</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>51</v>
@@ -7676,7 +7658,7 @@
         <v>156</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I220" s="2" t="s">
         <v>54</v>
@@ -7687,7 +7669,7 @@
         <v>30</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>51</v>
@@ -7705,7 +7687,7 @@
         <v>55</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I221" s="2" t="s">
         <v>54</v>
@@ -7716,7 +7698,7 @@
         <v>30</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>51</v>
@@ -7734,7 +7716,7 @@
         <v>55</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I222" s="2" t="s">
         <v>64</v>
@@ -7745,7 +7727,7 @@
         <v>30</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>51</v>
@@ -7763,7 +7745,7 @@
         <v>53</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I223" s="2" t="s">
         <v>54</v>
@@ -7844,7 +7826,7 @@
         <v>22</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>15</v>
@@ -7902,7 +7884,7 @@
         <v>22</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>15</v>
@@ -7989,7 +7971,7 @@
         <v>22</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>15</v>
@@ -8035,7 +8017,7 @@
         <v>9</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>11</v>
@@ -8064,7 +8046,7 @@
         <v>9</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>11</v>
@@ -8076,7 +8058,7 @@
         <v>22</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>15</v>
@@ -8093,7 +8075,7 @@
         <v>9</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>11</v>
@@ -8122,7 +8104,7 @@
         <v>9</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>11</v>
@@ -8151,7 +8133,7 @@
         <v>9</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>11</v>
@@ -8180,7 +8162,7 @@
         <v>9</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>11</v>
@@ -8192,7 +8174,7 @@
         <v>22</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>15</v>
@@ -8209,7 +8191,7 @@
         <v>9</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>11</v>
@@ -8279,7 +8261,7 @@
         <v>22</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>15</v>
@@ -8366,7 +8348,7 @@
         <v>22</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G244" s="1" t="s">
         <v>15</v>
@@ -8453,7 +8435,7 @@
         <v>22</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G247" s="1" t="s">
         <v>15</v>
@@ -8528,7 +8510,7 @@
         <v>9</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>11</v>
@@ -8557,7 +8539,7 @@
         <v>9</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>11</v>
@@ -8569,7 +8551,7 @@
         <v>22</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G251" s="1" t="s">
         <v>15</v>
@@ -8586,7 +8568,7 @@
         <v>9</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>11</v>
@@ -8656,7 +8638,7 @@
         <v>22</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G254" s="1" t="s">
         <v>15</v>
@@ -8801,7 +8783,7 @@
         <v>22</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G259" s="1" t="s">
         <v>15</v>
@@ -8859,7 +8841,7 @@
         <v>41</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G261" s="1" t="s">
         <v>15</v>
@@ -8888,7 +8870,7 @@
         <v>62</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="G262" s="1" t="s">
         <v>15</v>
@@ -8917,7 +8899,7 @@
         <v>39</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G263" s="1" t="s">
         <v>15</v>
@@ -9091,7 +9073,7 @@
         <v>45</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>133</v>
@@ -9120,7 +9102,7 @@
         <v>45</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>134</v>
@@ -9149,7 +9131,7 @@
         <v>45</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>135</v>
@@ -9178,7 +9160,7 @@
         <v>45</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>129</v>
@@ -9207,7 +9189,7 @@
         <v>45</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>136</v>
@@ -9236,7 +9218,7 @@
         <v>45</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>137</v>
@@ -9265,7 +9247,7 @@
         <v>62</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>138</v>
@@ -9294,7 +9276,7 @@
         <v>62</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>125</v>
@@ -9320,7 +9302,7 @@
         <v>140</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F277" s="2" t="s">
         <v>141</v>
@@ -9349,7 +9331,7 @@
         <v>140</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F278" s="2" t="s">
         <v>142</v>
@@ -9381,7 +9363,7 @@
         <v>58</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>125</v>
@@ -9468,7 +9450,7 @@
         <v>22</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G282" s="1" t="s">
         <v>15</v>
@@ -9555,7 +9537,7 @@
         <v>22</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>15</v>
@@ -9572,7 +9554,7 @@
         <v>171</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>11</v>
@@ -9601,7 +9583,7 @@
         <v>171</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>11</v>
@@ -9630,7 +9612,7 @@
         <v>171</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>11</v>
@@ -9642,7 +9624,7 @@
         <v>22</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G288" s="1" t="s">
         <v>15</v>
@@ -9659,7 +9641,7 @@
         <v>171</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>11</v>
@@ -9671,7 +9653,7 @@
         <v>117</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="G289" s="1" t="s">
         <v>15</v>
@@ -9688,7 +9670,7 @@
         <v>171</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>51</v>
@@ -9717,7 +9699,7 @@
         <v>171</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>51</v>
@@ -9746,7 +9728,7 @@
         <v>171</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>51</v>
@@ -9775,7 +9757,7 @@
         <v>171</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>51</v>
@@ -9804,7 +9786,7 @@
         <v>171</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>51</v>
@@ -9833,7 +9815,7 @@
         <v>171</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>51</v>
@@ -9845,7 +9827,7 @@
         <v>130</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>174</v>
@@ -9862,7 +9844,7 @@
         <v>171</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>51</v>
@@ -9891,7 +9873,7 @@
         <v>171</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>51</v>
@@ -9920,7 +9902,7 @@
         <v>171</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>51</v>
@@ -9949,7 +9931,7 @@
         <v>171</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>51</v>
@@ -9978,7 +9960,7 @@
         <v>171</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>51</v>
@@ -10007,7 +9989,7 @@
         <v>171</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>51</v>
@@ -10036,7 +10018,7 @@
         <v>171</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>51</v>
@@ -10065,7 +10047,7 @@
         <v>171</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>51</v>
@@ -10077,7 +10059,7 @@
         <v>183</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>186</v>
@@ -10094,7 +10076,7 @@
         <v>171</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>51</v>
@@ -10123,7 +10105,7 @@
         <v>171</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>51</v>
@@ -10152,7 +10134,7 @@
         <v>171</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>51</v>
@@ -10164,7 +10146,7 @@
         <v>61</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>189</v>
@@ -10181,7 +10163,7 @@
         <v>171</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>51</v>
@@ -10193,7 +10175,7 @@
         <v>61</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>134</v>
@@ -10210,7 +10192,7 @@
         <v>171</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>51</v>
@@ -10222,7 +10204,7 @@
         <v>61</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>190</v>
@@ -10239,7 +10221,7 @@
         <v>171</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>51</v>
@@ -10251,7 +10233,7 @@
         <v>61</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>135</v>
@@ -10268,7 +10250,7 @@
         <v>171</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>51</v>
@@ -10280,7 +10262,7 @@
         <v>61</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>191</v>
@@ -10297,7 +10279,7 @@
         <v>171</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>51</v>
@@ -10309,7 +10291,7 @@
         <v>61</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G311" s="1" t="s">
         <v>129</v>
@@ -10326,7 +10308,7 @@
         <v>171</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>51</v>
@@ -10338,7 +10320,7 @@
         <v>61</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>138</v>
@@ -10355,7 +10337,7 @@
         <v>171</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>51</v>
@@ -10367,7 +10349,7 @@
         <v>61</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>136</v>
@@ -10384,7 +10366,7 @@
         <v>171</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>51</v>
@@ -10396,7 +10378,7 @@
         <v>61</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>125</v>
@@ -10413,7 +10395,7 @@
         <v>171</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>51</v>
@@ -10425,7 +10407,7 @@
         <v>61</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>137</v>
@@ -10442,7 +10424,7 @@
         <v>171</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>51</v>
@@ -10471,7 +10453,7 @@
         <v>171</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>51</v>
@@ -10500,7 +10482,7 @@
         <v>171</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>51</v>
@@ -10529,7 +10511,7 @@
         <v>171</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>51</v>
@@ -10558,7 +10540,7 @@
         <v>171</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>51</v>
@@ -10587,7 +10569,7 @@
         <v>171</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>51</v>
@@ -10599,7 +10581,7 @@
         <v>86</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>173</v>
@@ -10616,7 +10598,7 @@
         <v>171</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>51</v>
@@ -10628,7 +10610,7 @@
         <v>86</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>137</v>
@@ -10645,7 +10627,7 @@
         <v>171</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>51</v>
@@ -10674,7 +10656,7 @@
         <v>30</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>51</v>
@@ -10703,7 +10685,7 @@
         <v>30</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>51</v>
@@ -10732,7 +10714,7 @@
         <v>30</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>51</v>
@@ -10744,7 +10726,7 @@
         <v>82</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G326" s="1" t="s">
         <v>83</v>
@@ -10761,7 +10743,7 @@
         <v>30</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>51</v>
@@ -10790,7 +10772,7 @@
         <v>30</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>51</v>
@@ -10802,7 +10784,7 @@
         <v>86</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>81</v>
@@ -10819,7 +10801,7 @@
         <v>30</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>51</v>
@@ -10831,7 +10813,7 @@
         <v>86</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>87</v>
@@ -10848,7 +10830,7 @@
         <v>30</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>51</v>
@@ -10877,7 +10859,7 @@
         <v>30</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>51</v>
@@ -10906,7 +10888,7 @@
         <v>30</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>51</v>
@@ -10976,7 +10958,7 @@
         <v>22</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>15</v>
@@ -11034,7 +11016,7 @@
         <v>41</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G336" s="1" t="s">
         <v>15</v>
@@ -11063,7 +11045,7 @@
         <v>39</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G337" s="1" t="s">
         <v>15</v>
@@ -11092,7 +11074,7 @@
         <v>62</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="G338" s="1" t="s">
         <v>15</v>
@@ -11121,7 +11103,7 @@
         <v>61</v>
       </c>
       <c r="F339" s="8" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>15</v>
@@ -11150,7 +11132,7 @@
         <v>45</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>15</v>
@@ -11179,7 +11161,7 @@
         <v>62</v>
       </c>
       <c r="F341" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>63</v>
@@ -11295,7 +11277,7 @@
         <v>22</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>15</v>
@@ -11353,7 +11335,7 @@
         <v>45</v>
       </c>
       <c r="F347" s="9" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G347" s="1" t="s">
         <v>15</v>
@@ -11382,7 +11364,7 @@
         <v>41</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G348" s="1" t="s">
         <v>15</v>
@@ -11411,7 +11393,7 @@
         <v>39</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G349" s="1" t="s">
         <v>15</v>
@@ -11440,7 +11422,7 @@
         <v>62</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="G350" s="1" t="s">
         <v>15</v>
@@ -11475,7 +11457,7 @@
         <v>55</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I351" s="2" t="s">
         <v>54</v>
@@ -11498,7 +11480,7 @@
         <v>62</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>63</v>
@@ -11591,7 +11573,7 @@
         <v>55</v>
       </c>
       <c r="H355" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I355" s="2" t="s">
         <v>54</v>
@@ -11620,7 +11602,7 @@
         <v>156</v>
       </c>
       <c r="H356" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I356" s="2" t="s">
         <v>54</v>
@@ -11649,7 +11631,7 @@
         <v>55</v>
       </c>
       <c r="H357" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I357" s="2" t="s">
         <v>54</v>
@@ -11678,7 +11660,7 @@
         <v>55</v>
       </c>
       <c r="H358" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I358" s="2" t="s">
         <v>64</v>
@@ -11707,7 +11689,7 @@
         <v>53</v>
       </c>
       <c r="H359" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I359" s="2" t="s">
         <v>54</v>
@@ -11759,7 +11741,7 @@
         <v>22</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G361" s="1" t="s">
         <v>15</v>
@@ -11817,7 +11799,7 @@
         <v>61</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="G363" s="1" t="s">
         <v>15</v>
@@ -11875,7 +11857,7 @@
         <v>61</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G365" s="1" t="s">
         <v>15</v>
@@ -11904,7 +11886,7 @@
         <v>41</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>15</v>
@@ -11933,7 +11915,7 @@
         <v>39</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>15</v>
@@ -11962,7 +11944,7 @@
         <v>62</v>
       </c>
       <c r="F368" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>15</v>
@@ -11997,7 +11979,7 @@
         <v>53</v>
       </c>
       <c r="H369" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I369" s="2" t="s">
         <v>54</v>
@@ -12026,7 +12008,7 @@
         <v>156</v>
       </c>
       <c r="H370" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I370" s="2" t="s">
         <v>54</v>
@@ -12055,7 +12037,7 @@
         <v>55</v>
       </c>
       <c r="H371" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I371" s="2" t="s">
         <v>54</v>
@@ -12142,7 +12124,7 @@
         <v>55</v>
       </c>
       <c r="H374" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I374" s="2" t="s">
         <v>54</v>
@@ -12165,7 +12147,7 @@
         <v>62</v>
       </c>
       <c r="F375" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>63</v>
@@ -12200,7 +12182,7 @@
         <v>55</v>
       </c>
       <c r="H376" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I376" s="2" t="s">
         <v>54</v>
@@ -12229,7 +12211,7 @@
         <v>55</v>
       </c>
       <c r="H377" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I377" s="2" t="s">
         <v>64</v>
@@ -12252,7 +12234,7 @@
         <v>22</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G378" s="1" t="s">
         <v>15</v>
@@ -12339,7 +12321,7 @@
         <v>22</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G381" s="1" t="s">
         <v>15</v>
@@ -12426,7 +12408,7 @@
         <v>19</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="G384" s="1" t="s">
         <v>15</v>
@@ -12484,7 +12466,7 @@
         <v>85</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="G386" s="1" t="s">
         <v>15</v>
@@ -12513,7 +12495,7 @@
         <v>45</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="G387" s="1" t="s">
         <v>15</v>
@@ -12542,7 +12524,7 @@
         <v>22</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G388" s="1" t="s">
         <v>15</v>
@@ -12658,7 +12640,7 @@
         <v>22</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>15</v>
@@ -12716,7 +12698,7 @@
         <v>39</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G394" s="1" t="s">
         <v>15</v>
@@ -12745,7 +12727,7 @@
         <v>41</v>
       </c>
       <c r="F395" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G395" s="1" t="s">
         <v>15</v>
@@ -12774,7 +12756,7 @@
         <v>61</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="G396" s="1" t="s">
         <v>15</v>
@@ -12832,7 +12814,7 @@
         <v>61</v>
       </c>
       <c r="F398" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G398" s="1" t="s">
         <v>15</v>
@@ -12861,7 +12843,7 @@
         <v>62</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>15</v>
@@ -12919,7 +12901,7 @@
         <v>39</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>15</v>
@@ -12948,7 +12930,7 @@
         <v>29</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="G402" s="1" t="s">
         <v>15</v>
@@ -13006,7 +12988,7 @@
         <v>62</v>
       </c>
       <c r="F404" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>63</v>
@@ -13099,7 +13081,7 @@
         <v>55</v>
       </c>
       <c r="H407" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I407" s="2" t="s">
         <v>54</v>
@@ -13128,7 +13110,7 @@
         <v>55</v>
       </c>
       <c r="H408" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I408" s="2" t="s">
         <v>54</v>
@@ -13157,7 +13139,7 @@
         <v>55</v>
       </c>
       <c r="H409" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I409" s="2" t="s">
         <v>64</v>
@@ -13186,7 +13168,7 @@
         <v>53</v>
       </c>
       <c r="H410" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I410" s="2" t="s">
         <v>54</v>
@@ -13238,7 +13220,7 @@
         <v>22</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>15</v>
@@ -13325,7 +13307,7 @@
         <v>39</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G415" s="1" t="s">
         <v>15</v>
@@ -13354,7 +13336,7 @@
         <v>41</v>
       </c>
       <c r="F416" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G416" s="1" t="s">
         <v>15</v>
@@ -13383,7 +13365,7 @@
         <v>61</v>
       </c>
       <c r="F417" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="G417" s="1" t="s">
         <v>15</v>
@@ -13441,7 +13423,7 @@
         <v>61</v>
       </c>
       <c r="F419" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G419" s="1" t="s">
         <v>15</v>
@@ -13470,7 +13452,7 @@
         <v>62</v>
       </c>
       <c r="F420" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="G420" s="1" t="s">
         <v>15</v>
@@ -13528,7 +13510,7 @@
         <v>39</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G422" s="1" t="s">
         <v>15</v>
@@ -13557,7 +13539,7 @@
         <v>62</v>
       </c>
       <c r="F423" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>63</v>
@@ -13650,7 +13632,7 @@
         <v>55</v>
       </c>
       <c r="H426" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I426" s="2" t="s">
         <v>54</v>
@@ -13679,7 +13661,7 @@
         <v>55</v>
       </c>
       <c r="H427" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I427" s="2" t="s">
         <v>54</v>
@@ -13708,7 +13690,7 @@
         <v>55</v>
       </c>
       <c r="H428" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I428" s="2" t="s">
         <v>64</v>
@@ -13737,30 +13719,30 @@
         <v>53</v>
       </c>
       <c r="H429" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I429" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="430" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
-        <v>214</v>
+        <v>171</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>215</v>
+        <v>302</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D430" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E430" s="2" t="s">
-        <v>22</v>
+      <c r="D430" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E430" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>257</v>
+        <v>214</v>
       </c>
       <c r="G430" s="1" t="s">
         <v>15</v>
@@ -13774,22 +13756,22 @@
     </row>
     <row r="431" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
-        <v>214</v>
+        <v>171</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>216</v>
+        <v>302</v>
       </c>
       <c r="C431" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>257</v>
+        <v>215</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>15</v>
@@ -13802,11 +13784,11 @@
       </c>
     </row>
     <row r="432" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A432" s="1" t="s">
-        <v>214</v>
+      <c r="A432" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>307</v>
+        <v>92</v>
       </c>
       <c r="C432" s="2" t="s">
         <v>11</v>
@@ -13818,7 +13800,7 @@
         <v>22</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="G432" s="1" t="s">
         <v>15</v>
@@ -13831,23 +13813,23 @@
       </c>
     </row>
     <row r="433" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A433" s="1" t="s">
-        <v>214</v>
+      <c r="A433" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>217</v>
+        <v>92</v>
       </c>
       <c r="C433" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D433" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E433" s="2" t="s">
-        <v>22</v>
+      <c r="D433" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E433" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>257</v>
+        <v>68</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>15</v>
@@ -13860,23 +13842,23 @@
       </c>
     </row>
     <row r="434" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A434" s="1" t="s">
-        <v>214</v>
+      <c r="A434" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>218</v>
+        <v>92</v>
       </c>
       <c r="C434" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D434" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E434" s="2" t="s">
-        <v>22</v>
+      <c r="D434" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E434" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>257</v>
+        <v>69</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>15</v>
@@ -13888,24 +13870,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="435" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A435" s="1" t="s">
-        <v>171</v>
+    <row r="435" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A435" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>308</v>
+        <v>92</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D435" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E435" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F435" s="1" t="s">
-        <v>219</v>
+      <c r="D435" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E435" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F435" s="2" t="s">
+        <v>258</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>15</v>
@@ -13918,23 +13900,23 @@
       </c>
     </row>
     <row r="436" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A436" s="1" t="s">
-        <v>171</v>
+      <c r="A436" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>308</v>
+        <v>92</v>
       </c>
       <c r="C436" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E436" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F436" s="1" t="s">
-        <v>220</v>
+        <v>71</v>
+      </c>
+      <c r="F436" s="2" t="s">
+        <v>259</v>
       </c>
       <c r="G436" s="1" t="s">
         <v>15</v>
@@ -13957,13 +13939,13 @@
         <v>11</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E437" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F437" s="1" t="s">
-        <v>253</v>
+        <v>29</v>
+      </c>
+      <c r="F437" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="G437" s="1" t="s">
         <v>15</v>
@@ -13985,14 +13967,14 @@
       <c r="C438" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D438" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E438" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F438" s="1" t="s">
-        <v>68</v>
+      <c r="D438" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E438" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F438" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="G438" s="1" t="s">
         <v>15</v>
@@ -14012,25 +13994,25 @@
         <v>92</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D439" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E439" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F439" s="1" t="s">
-        <v>69</v>
+        <v>51</v>
+      </c>
+      <c r="D439" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E439" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F439" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="G439" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H439" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I439" s="1" t="s">
-        <v>17</v>
+        <v>75</v>
+      </c>
+      <c r="H439" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I439" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="440" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -14041,25 +14023,25 @@
         <v>92</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F440" s="2" t="s">
-        <v>263</v>
+        <v>78</v>
       </c>
       <c r="G440" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H440" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I440" s="1" t="s">
-        <v>17</v>
+        <v>75</v>
+      </c>
+      <c r="H440" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I440" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="441" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -14070,25 +14052,25 @@
         <v>92</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F441" s="2" t="s">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="G441" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H441" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I441" s="1" t="s">
-        <v>17</v>
+        <v>75</v>
+      </c>
+      <c r="H441" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I441" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="442" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -14099,25 +14081,25 @@
         <v>92</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="F442" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G442" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H442" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I442" s="1" t="s">
-        <v>17</v>
+        <v>81</v>
+      </c>
+      <c r="H442" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I442" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="443" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -14128,25 +14110,25 @@
         <v>92</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F443" s="2" t="s">
-        <v>74</v>
+        <v>260</v>
       </c>
       <c r="G443" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H443" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I443" s="1" t="s">
-        <v>17</v>
+        <v>83</v>
+      </c>
+      <c r="H443" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I443" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="444" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -14160,16 +14142,16 @@
         <v>51</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F444" s="2" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="G444" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H444" s="1" t="s">
         <v>76</v>
@@ -14189,16 +14171,16 @@
         <v>51</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F445" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
+      </c>
+      <c r="F445" s="1" t="s">
+        <v>261</v>
       </c>
       <c r="G445" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H445" s="1" t="s">
         <v>76</v>
@@ -14218,19 +14200,19 @@
         <v>51</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F446" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G446" s="1" t="s">
-        <v>75</v>
+        <v>86</v>
+      </c>
+      <c r="F446" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="G446" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="H446" s="1" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="I446" s="2" t="s">
         <v>54</v>
@@ -14247,16 +14229,16 @@
         <v>51</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F447" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G447" s="1" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H447" s="1" t="s">
         <v>76</v>
@@ -14276,16 +14258,16 @@
         <v>51</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E448" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F448" s="2" t="s">
-        <v>265</v>
+        <v>88</v>
+      </c>
+      <c r="F448" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="G448" s="1" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H448" s="1" t="s">
         <v>76</v>
@@ -14296,205 +14278,205 @@
     </row>
     <row r="449" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B449" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C449" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D449" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E449" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F449" s="2" t="s">
-        <v>84</v>
+        <v>9</v>
+      </c>
+      <c r="B449" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C449" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D449" t="s">
+        <v>241</v>
+      </c>
+      <c r="E449" t="s">
+        <v>241</v>
+      </c>
+      <c r="F449" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="G449" s="1" t="s">
-        <v>83</v>
+        <v>241</v>
       </c>
       <c r="H449" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I449" s="2" t="s">
-        <v>54</v>
+        <v>241</v>
+      </c>
+      <c r="I449" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="450" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B450" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C450" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D450" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E450" s="2" t="s">
-        <v>86</v>
+        <v>9</v>
+      </c>
+      <c r="B450" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C450" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D450" t="s">
+        <v>241</v>
+      </c>
+      <c r="E450" t="s">
+        <v>241</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="G450" s="1" t="s">
-        <v>81</v>
+        <v>241</v>
       </c>
       <c r="H450" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I450" s="2" t="s">
-        <v>54</v>
+        <v>241</v>
+      </c>
+      <c r="I450" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="451" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B451" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C451" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D451" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E451" s="2" t="s">
-        <v>86</v>
+      <c r="B451" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C451" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D451" t="s">
+        <v>241</v>
+      </c>
+      <c r="E451" t="s">
+        <v>241</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="G451" s="2" t="s">
-        <v>87</v>
+        <v>241</v>
+      </c>
+      <c r="G451" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="H451" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I451" s="2" t="s">
-        <v>54</v>
+        <v>241</v>
+      </c>
+      <c r="I451" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="452" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B452" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C452" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D452" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E452" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F452" s="2" t="s">
-        <v>89</v>
+      <c r="B452" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C452" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D452" t="s">
+        <v>241</v>
+      </c>
+      <c r="E452" t="s">
+        <v>241</v>
+      </c>
+      <c r="F452" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="G452" s="1" t="s">
-        <v>90</v>
+        <v>241</v>
       </c>
       <c r="H452" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I452" s="2" t="s">
-        <v>54</v>
+        <v>241</v>
+      </c>
+      <c r="I452" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="453" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B453" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C453" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D453" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E453" s="2" t="s">
-        <v>88</v>
+        <v>9</v>
+      </c>
+      <c r="B453" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C453" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D453" t="s">
+        <v>241</v>
+      </c>
+      <c r="E453" t="s">
+        <v>241</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>91</v>
+        <v>241</v>
       </c>
       <c r="G453" s="1" t="s">
-        <v>63</v>
+        <v>241</v>
       </c>
       <c r="H453" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I453" s="2" t="s">
-        <v>54</v>
+        <v>241</v>
+      </c>
+      <c r="I453" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="454" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D454" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E454" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G454" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H454" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I454" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="455" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>254</v>
+        <v>92</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D455" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E455" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G455" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H455" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I455" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="456" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -14502,28 +14484,28 @@
         <v>30</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>31</v>
+        <v>263</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D456" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E456" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G456" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H456" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I456" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="457" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -14531,28 +14513,28 @@
         <v>30</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D457" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E457" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F457" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G457" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H457" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I457" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="458" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -14560,144 +14542,144 @@
         <v>9</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D458" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E458" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G458" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H458" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I458" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="459" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D459" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E459" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F459" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G459" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H459" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I459" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="460" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D460" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E460" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F460" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G460" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H460" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I460" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="461" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>268</v>
+        <v>120</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D461" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E461" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G461" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H461" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I461" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="462" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D462" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E462" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F462" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G462" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H462" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I462" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="463" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -14705,28 +14687,28 @@
         <v>9</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D463" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E463" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G463" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H463" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I463" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="464" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -14734,28 +14716,28 @@
         <v>9</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="C464" s="1" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D464" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E464" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F464" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G464" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H464" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I464" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="465" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -14763,28 +14745,28 @@
         <v>9</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D465" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E465" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F465" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G465" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H465" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I465" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="466" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -14792,57 +14774,57 @@
         <v>9</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="C466" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D466" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E466" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F466" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G466" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H466" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I466" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="467" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="C467" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D467" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E467" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G467" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H467" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I467" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="468" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -14850,28 +14832,28 @@
         <v>9</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C468" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D468" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E468" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G468" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H468" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I468" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="469" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -14879,115 +14861,115 @@
         <v>9</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D469" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E469" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G469" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H469" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I469" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="470" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>146</v>
+        <v>277</v>
       </c>
       <c r="C470" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D470" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E470" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G470" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H470" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I470" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="471" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>147</v>
+        <v>279</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D471" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E471" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G471" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H471" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I471" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="472" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C472" s="1" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D472" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E472" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F472" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G472" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H472" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I472" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="473" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -14995,28 +14977,28 @@
         <v>9</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C473" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D473" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E473" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F473" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G473" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H473" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I473" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="474" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -15024,86 +15006,86 @@
         <v>9</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C474" s="1" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D474" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E474" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F474" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G474" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H474" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I474" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="475" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>282</v>
+        <v>306</v>
       </c>
       <c r="C475" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D475" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E475" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F475" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G475" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H475" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I475" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="476" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C476" s="1" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D476" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E476" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F476" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G476" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H476" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I476" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="477" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -15111,28 +15093,28 @@
         <v>9</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C477" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D477" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E477" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F477" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G477" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H477" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I477" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="478" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -15140,28 +15122,28 @@
         <v>9</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D478" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E478" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F478" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G478" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H478" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I478" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="479" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -15169,28 +15151,28 @@
         <v>9</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D479" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E479" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F479" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G479" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H479" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I479" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="480" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -15198,28 +15180,28 @@
         <v>9</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>312</v>
+        <v>281</v>
       </c>
       <c r="C480" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D480" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E480" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F480" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G480" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H480" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I480" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="481" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -15227,28 +15209,28 @@
         <v>9</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>285</v>
+        <v>167</v>
       </c>
       <c r="C481" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D481" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E481" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F481" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G481" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H481" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I481" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="482" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -15256,28 +15238,28 @@
         <v>9</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C482" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D482" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E482" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F482" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G482" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H482" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I482" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="483" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -15285,28 +15267,28 @@
         <v>9</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D483" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E483" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F483" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G483" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H483" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I483" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="484" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -15314,202 +15296,202 @@
         <v>9</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D484" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E484" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F484" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G484" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H484" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I484" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="485" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>9</v>
+        <v>171</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D485" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E485" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F485" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G485" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H485" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I485" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="486" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D486" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E486" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F486" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G486" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H486" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I486" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="487" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D487" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E487" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F487" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G487" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H487" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I487" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="488" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D488" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E488" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F488" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G488" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H488" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I488" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="489" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D489" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E489" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F489" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G489" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H489" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I489" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="490" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
-        <v>171</v>
+        <v>30</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>287</v>
+        <v>205</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="D490" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E490" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F490" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G490" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H490" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I490" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="491" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -15517,28 +15499,28 @@
         <v>30</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D491" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E491" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F491" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G491" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H491" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I491" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="492" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -15546,28 +15528,28 @@
         <v>30</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D492" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E492" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F492" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G492" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H492" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I492" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="493" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -15575,115 +15557,115 @@
         <v>30</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D493" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E493" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F493" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G493" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H493" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I493" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="494" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A494" s="2" t="s">
-        <v>30</v>
+      <c r="A494" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>204</v>
+        <v>302</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D494" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E494" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F494" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G494" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H494" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I494" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="495" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>205</v>
+        <v>10</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D495" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E495" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F495" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G495" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H495" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I495" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="496" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>207</v>
+        <v>249</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D496" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E496" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F496" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G496" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H496" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I496" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="497" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -15691,28 +15673,28 @@
         <v>30</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>208</v>
+        <v>31</v>
       </c>
       <c r="C497" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D497" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E497" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F497" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G497" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H497" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I497" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="498" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -15720,202 +15702,202 @@
         <v>30</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>211</v>
+        <v>56</v>
       </c>
       <c r="C498" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D498" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E498" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F498" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G498" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H498" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I498" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="499" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
-        <v>214</v>
+        <v>9</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>215</v>
+        <v>65</v>
       </c>
       <c r="C499" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D499" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E499" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F499" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G499" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H499" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I499" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="500" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
-        <v>214</v>
+        <v>30</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>216</v>
+        <v>67</v>
       </c>
       <c r="C500" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D500" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E500" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F500" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G500" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H500" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I500" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="501" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
-        <v>214</v>
+        <v>30</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>307</v>
+        <v>92</v>
       </c>
       <c r="C501" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D501" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E501" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F501" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G501" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H501" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I501" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="502" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>214</v>
+        <v>30</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>217</v>
+        <v>263</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D502" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E502" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F502" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G502" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H502" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I502" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="503" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
-        <v>214</v>
+        <v>30</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>218</v>
+        <v>95</v>
       </c>
       <c r="C503" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D503" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E503" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F503" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G503" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H503" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I503" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="504" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A504" s="1" t="s">
-        <v>171</v>
+      <c r="A504" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>308</v>
+        <v>111</v>
       </c>
       <c r="C504" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D504" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E504" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F504" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G504" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H504" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I504" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="505" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -15923,28 +15905,28 @@
         <v>9</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>10</v>
+        <v>113</v>
       </c>
       <c r="C505" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D505" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E505" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F505" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G505" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H505" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I505" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="506" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -15952,86 +15934,86 @@
         <v>9</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>254</v>
+        <v>119</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D506" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E506" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F506" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G506" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H506" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I506" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="507" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>31</v>
+        <v>120</v>
       </c>
       <c r="C507" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D507" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E507" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F507" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G507" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H507" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I507" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="508" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="C508" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D508" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E508" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F508" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G508" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H508" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I508" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="509" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -16039,115 +16021,115 @@
         <v>9</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>65</v>
+        <v>144</v>
       </c>
       <c r="C509" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D509" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E509" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F509" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G509" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H509" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I509" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="510" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>67</v>
+        <v>145</v>
       </c>
       <c r="C510" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D510" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E510" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F510" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G510" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H510" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I510" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="511" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>92</v>
+        <v>146</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D511" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E511" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F511" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G511" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H511" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I511" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="512" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>268</v>
+        <v>147</v>
       </c>
       <c r="C512" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D512" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E512" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F512" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G512" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H512" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I512" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="513" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -16155,28 +16137,28 @@
         <v>30</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="C513" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D513" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E513" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F513" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G513" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H513" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I513" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="514" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -16184,28 +16166,28 @@
         <v>9</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="C514" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D514" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E514" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F514" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G514" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H514" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I514" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="515" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -16213,86 +16195,86 @@
         <v>9</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="C515" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D515" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E515" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F515" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G515" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H515" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I515" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="516" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>119</v>
+        <v>277</v>
       </c>
       <c r="C516" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D516" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E516" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F516" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G516" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H516" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I516" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="517" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>120</v>
+        <v>279</v>
       </c>
       <c r="C517" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D517" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E517" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F517" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G517" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H517" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I517" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="518" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -16300,28 +16282,28 @@
         <v>9</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="C518" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D518" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E518" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F518" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G518" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H518" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I518" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="519" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -16329,28 +16311,28 @@
         <v>9</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="C519" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D519" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E519" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F519" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G519" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H519" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I519" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="520" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -16358,28 +16340,28 @@
         <v>9</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="C520" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D520" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E520" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F520" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G520" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H520" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I520" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="521" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -16387,28 +16369,28 @@
         <v>9</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>146</v>
+        <v>306</v>
       </c>
       <c r="C521" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D521" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E521" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F521" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G521" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H521" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I521" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="522" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -16416,57 +16398,57 @@
         <v>9</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>147</v>
+        <v>280</v>
       </c>
       <c r="C522" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D522" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E522" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F522" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G522" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H522" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I522" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="523" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="C523" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D523" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E523" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F523" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G523" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H523" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I523" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="524" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -16474,28 +16456,28 @@
         <v>9</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="C524" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D524" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E524" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F524" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G524" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H524" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I524" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="525" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -16503,86 +16485,86 @@
         <v>9</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C525" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D525" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E525" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F525" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G525" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H525" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I525" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="526" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C526" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D526" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E526" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F526" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G526" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H526" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I526" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="527" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>284</v>
+        <v>167</v>
       </c>
       <c r="C527" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D527" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E527" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F527" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G527" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H527" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I527" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="528" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -16590,28 +16572,28 @@
         <v>9</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C528" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D528" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E528" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F528" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G528" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H528" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I528" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="529" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -16619,28 +16601,28 @@
         <v>9</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="C529" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D529" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E529" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F529" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G529" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H529" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I529" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="530" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
@@ -16648,780 +16630,435 @@
         <v>9</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D530" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E530" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F530" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G530" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H530" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I530" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="531" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
-        <v>9</v>
+        <v>171</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>312</v>
+        <v>282</v>
       </c>
       <c r="C531" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D531" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E531" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F531" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G531" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H531" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I531" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="532" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>285</v>
+        <v>199</v>
       </c>
       <c r="C532" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D532" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E532" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F532" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G532" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H532" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I532" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="533" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="C533" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D533" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E533" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F533" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G533" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H533" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I533" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="534" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D534" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E534" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F534" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G534" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H534" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I534" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="535" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>165</v>
+        <v>204</v>
       </c>
       <c r="C535" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D535" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E535" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F535" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G535" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H535" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I535" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="536" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>286</v>
+        <v>205</v>
       </c>
       <c r="C536" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D536" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E536" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F536" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G536" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H536" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I536" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="537" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>167</v>
+        <v>207</v>
       </c>
       <c r="C537" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D537" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E537" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F537" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G537" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H537" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I537" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="538" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="C538" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D538" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E538" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F538" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G538" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H538" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I538" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="539" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c r="C539" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D539" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E539" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F539" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G539" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H539" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I539" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="540" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A540" s="2" t="s">
-        <v>9</v>
+      <c r="A540" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>170</v>
+        <v>302</v>
       </c>
       <c r="C540" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D540" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E540" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F540" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G540" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H540" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I540" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="541" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A541" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B541" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C541" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D541" t="s">
-        <v>246</v>
-      </c>
-      <c r="E541" t="s">
-        <v>246</v>
-      </c>
-      <c r="F541" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G541" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H541" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I541" t="s">
-        <v>246</v>
-      </c>
+      <c r="B541" s="1"/>
+      <c r="F541" s="1"/>
+      <c r="G541" s="1"/>
+      <c r="H541" s="1"/>
     </row>
     <row r="542" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A542" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B542" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C542" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D542" t="s">
-        <v>246</v>
-      </c>
-      <c r="E542" t="s">
-        <v>246</v>
-      </c>
-      <c r="F542" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G542" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H542" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I542" t="s">
-        <v>246</v>
-      </c>
+      <c r="B542" s="1"/>
+      <c r="F542" s="1"/>
+      <c r="G542" s="1"/>
+      <c r="H542" s="1"/>
     </row>
     <row r="543" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A543" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B543" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C543" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D543" t="s">
-        <v>246</v>
-      </c>
-      <c r="E543" t="s">
-        <v>246</v>
-      </c>
-      <c r="F543" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G543" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H543" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I543" t="s">
-        <v>246</v>
-      </c>
+      <c r="B543" s="1"/>
+      <c r="F543" s="1"/>
+      <c r="G543" s="1"/>
+      <c r="H543" s="1"/>
     </row>
     <row r="544" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A544" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B544" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C544" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D544" t="s">
-        <v>246</v>
-      </c>
-      <c r="E544" t="s">
-        <v>246</v>
-      </c>
-      <c r="F544" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G544" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H544" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I544" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="545" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A545" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B545" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C545" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D545" t="s">
-        <v>246</v>
-      </c>
-      <c r="E545" t="s">
-        <v>246</v>
-      </c>
-      <c r="F545" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G545" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H545" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I545" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="546" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A546" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B546" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C546" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D546" t="s">
-        <v>246</v>
-      </c>
-      <c r="E546" t="s">
-        <v>246</v>
-      </c>
-      <c r="F546" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G546" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H546" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I546" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="547" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A547" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B547" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C547" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D547" t="s">
-        <v>246</v>
-      </c>
-      <c r="E547" t="s">
-        <v>246</v>
-      </c>
-      <c r="F547" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G547" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H547" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I547" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="548" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A548" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B548" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C548" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D548" t="s">
-        <v>246</v>
-      </c>
-      <c r="E548" t="s">
-        <v>246</v>
-      </c>
-      <c r="F548" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G548" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H548" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I548" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="549" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A549" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B549" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C549" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D549" t="s">
-        <v>246</v>
-      </c>
-      <c r="E549" t="s">
-        <v>246</v>
-      </c>
-      <c r="F549" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G549" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H549" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I549" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="550" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A550" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B550" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C550" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D550" t="s">
-        <v>246</v>
-      </c>
-      <c r="E550" t="s">
-        <v>246</v>
-      </c>
-      <c r="F550" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G550" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H550" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I550" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="551" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A551" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B551" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C551" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D551" t="s">
-        <v>246</v>
-      </c>
-      <c r="E551" t="s">
-        <v>246</v>
-      </c>
-      <c r="F551" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G551" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H551" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I551" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="552" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A552" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B552" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="C552" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D552" t="s">
-        <v>246</v>
-      </c>
-      <c r="E552" t="s">
-        <v>246</v>
-      </c>
-      <c r="F552" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G552" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H552" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I552" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="553" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A553" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B553" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C553" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D553" t="s">
-        <v>246</v>
-      </c>
-      <c r="E553" t="s">
-        <v>246</v>
-      </c>
-      <c r="F553" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G553" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H553" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I553" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="554" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A554" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B554" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C554" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D554" t="s">
-        <v>246</v>
-      </c>
-      <c r="E554" t="s">
-        <v>246</v>
-      </c>
-      <c r="F554" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G554" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H554" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I554" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="555" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A555" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B555" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C555" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D555" t="s">
-        <v>246</v>
-      </c>
-      <c r="E555" t="s">
-        <v>246</v>
-      </c>
-      <c r="F555" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="G555" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H555" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I555" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="556" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B544" s="1"/>
+      <c r="F544" s="1"/>
+      <c r="G544" s="1"/>
+      <c r="H544" s="1"/>
+    </row>
+    <row r="545" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B545" s="1"/>
+      <c r="F545" s="1"/>
+      <c r="G545" s="1"/>
+      <c r="H545" s="1"/>
+    </row>
+    <row r="546" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B546" s="1"/>
+      <c r="F546" s="1"/>
+      <c r="G546" s="1"/>
+      <c r="H546" s="1"/>
+    </row>
+    <row r="547" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B547" s="1"/>
+      <c r="F547" s="1"/>
+      <c r="G547" s="1"/>
+      <c r="H547" s="1"/>
+    </row>
+    <row r="548" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B548" s="1"/>
+      <c r="F548" s="1"/>
+      <c r="G548" s="1"/>
+      <c r="H548" s="1"/>
+    </row>
+    <row r="549" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B549" s="1"/>
+      <c r="F549" s="1"/>
+      <c r="G549" s="1"/>
+      <c r="H549" s="1"/>
+    </row>
+    <row r="550" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B550" s="1"/>
+      <c r="F550" s="1"/>
+      <c r="G550" s="1"/>
+      <c r="H550" s="1"/>
+    </row>
+    <row r="551" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B551" s="1"/>
+      <c r="F551" s="1"/>
+      <c r="G551" s="1"/>
+      <c r="H551" s="1"/>
+    </row>
+    <row r="552" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B552" s="1"/>
+      <c r="F552" s="1"/>
+      <c r="G552" s="1"/>
+      <c r="H552" s="1"/>
+    </row>
+    <row r="553" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B553" s="1"/>
+      <c r="F553" s="1"/>
+      <c r="G553" s="1"/>
+      <c r="H553" s="1"/>
+    </row>
+    <row r="554" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B554" s="1"/>
+      <c r="F554" s="1"/>
+      <c r="G554" s="1"/>
+      <c r="H554" s="1"/>
+    </row>
+    <row r="555" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B555" s="1"/>
+      <c r="F555" s="1"/>
+      <c r="G555" s="1"/>
+      <c r="H555" s="1"/>
+    </row>
+    <row r="556" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B556" s="1"/>
       <c r="F556" s="1"/>
       <c r="G556" s="1"/>
       <c r="H556" s="1"/>
     </row>
-    <row r="557" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="557" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B557" s="1"/>
       <c r="F557" s="1"/>
       <c r="G557" s="1"/>
       <c r="H557" s="1"/>
     </row>
-    <row r="558" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="558" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B558" s="1"/>
       <c r="F558" s="1"/>
       <c r="G558" s="1"/>
       <c r="H558" s="1"/>
     </row>
-    <row r="559" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="559" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B559" s="1"/>
       <c r="F559" s="1"/>
       <c r="G559" s="1"/>
       <c r="H559" s="1"/>
     </row>
-    <row r="560" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="560" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B560" s="1"/>
       <c r="F560" s="1"/>
       <c r="G560" s="1"/>
@@ -22689,98 +22326,8 @@
       <c r="G1437" s="1"/>
       <c r="H1437" s="1"/>
     </row>
-    <row r="1438" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B1438" s="1"/>
-      <c r="F1438" s="1"/>
-      <c r="G1438" s="1"/>
-      <c r="H1438" s="1"/>
-    </row>
-    <row r="1439" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B1439" s="1"/>
-      <c r="F1439" s="1"/>
-      <c r="G1439" s="1"/>
-      <c r="H1439" s="1"/>
-    </row>
-    <row r="1440" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B1440" s="1"/>
-      <c r="F1440" s="1"/>
-      <c r="G1440" s="1"/>
-      <c r="H1440" s="1"/>
-    </row>
-    <row r="1441" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B1441" s="1"/>
-      <c r="F1441" s="1"/>
-      <c r="G1441" s="1"/>
-      <c r="H1441" s="1"/>
-    </row>
-    <row r="1442" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B1442" s="1"/>
-      <c r="F1442" s="1"/>
-      <c r="G1442" s="1"/>
-      <c r="H1442" s="1"/>
-    </row>
-    <row r="1443" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B1443" s="1"/>
-      <c r="F1443" s="1"/>
-      <c r="G1443" s="1"/>
-      <c r="H1443" s="1"/>
-    </row>
-    <row r="1444" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B1444" s="1"/>
-      <c r="F1444" s="1"/>
-      <c r="G1444" s="1"/>
-      <c r="H1444" s="1"/>
-    </row>
-    <row r="1445" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B1445" s="1"/>
-      <c r="F1445" s="1"/>
-      <c r="G1445" s="1"/>
-      <c r="H1445" s="1"/>
-    </row>
-    <row r="1446" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B1446" s="1"/>
-      <c r="F1446" s="1"/>
-      <c r="G1446" s="1"/>
-      <c r="H1446" s="1"/>
-    </row>
-    <row r="1447" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B1447" s="1"/>
-      <c r="F1447" s="1"/>
-      <c r="G1447" s="1"/>
-      <c r="H1447" s="1"/>
-    </row>
-    <row r="1448" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B1448" s="1"/>
-      <c r="F1448" s="1"/>
-      <c r="G1448" s="1"/>
-      <c r="H1448" s="1"/>
-    </row>
-    <row r="1449" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B1449" s="1"/>
-      <c r="F1449" s="1"/>
-      <c r="G1449" s="1"/>
-      <c r="H1449" s="1"/>
-    </row>
-    <row r="1450" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B1450" s="1"/>
-      <c r="F1450" s="1"/>
-      <c r="G1450" s="1"/>
-      <c r="H1450" s="1"/>
-    </row>
-    <row r="1451" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B1451" s="1"/>
-      <c r="F1451" s="1"/>
-      <c r="G1451" s="1"/>
-      <c r="H1451" s="1"/>
-    </row>
-    <row r="1452" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B1452" s="1"/>
-      <c r="F1452" s="1"/>
-      <c r="G1452" s="1"/>
-      <c r="H1452" s="1"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I555" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I540" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -22793,33 +22340,33 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>227</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D2" s="13">
         <v>50</v>
@@ -22828,18 +22375,18 @@
         <v>360</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>51</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D3" s="13">
         <v>350</v>
@@ -22848,18 +22395,18 @@
         <v>360</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D4" s="13">
         <v>697</v>
@@ -22868,18 +22415,18 @@
         <v>136</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>43</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D5" s="13">
         <v>688</v>
@@ -22888,18 +22435,18 @@
         <v>591</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D6" s="13">
         <v>1050</v>
@@ -22908,18 +22455,18 @@
         <v>360</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D7" s="13">
         <v>1350</v>
@@ -22928,18 +22475,18 @@
         <v>160</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D8" s="13">
         <v>1350</v>
@@ -22948,18 +22495,18 @@
         <v>240</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D9" s="13">
         <v>1350</v>
@@ -22968,18 +22515,18 @@
         <v>320</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D10" s="13">
         <v>1350</v>
@@ -22988,18 +22535,18 @@
         <v>400</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D11" s="13">
         <v>1350</v>
@@ -23008,18 +22555,18 @@
         <v>480</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D12" s="13">
         <v>701</v>
@@ -23028,7 +22575,7 @@
         <v>359</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
